--- a/SORT PIVOT AND TRANSFORM DATA IN EXCEL/pivot-ex.xlsx
+++ b/SORT PIVOT AND TRANSFORM DATA IN EXCEL/pivot-ex.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10410"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adamorse/Documents/Learn DA with Excel/exploring data/exercises/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CODECADEMY 2024\EXCEL BASICS\SORT PIVOT AND TRANSFORM DATA IN EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29FAB890-48EF-F843-84D0-BB423087962A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D83A2C3-FA7B-496B-9085-16BE12DA90C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15800" xr2:uid="{21A08B8F-33A6-C748-B43F-55333DB6253A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{21A08B8F-33A6-C748-B43F-55333DB6253A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,35 +25,26 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="78" r:id="rId10"/>
+    <pivotCache cacheId="8" r:id="rId10"/>
+    <pivotCache cacheId="13" r:id="rId11"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -68,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="33">
   <si>
     <t>Codecademy: Learn Excel for Data Analysis</t>
   </si>
@@ -156,12 +147,24 @@
   <si>
     <t>We've already loaded a dataset for you to use (below). Create a pivot table in H3 on this sheet. The pivot table you create should answer the following question: what is the maximum number of book titles per capita for each country? (Hint: you don't need to specify column labels.)</t>
   </si>
+  <si>
+    <t>Названия столбцов</t>
+  </si>
+  <si>
+    <t>Общий итог</t>
+  </si>
+  <si>
+    <t>Названия строк</t>
+  </si>
+  <si>
+    <t>Среднее по полю Book titles per capita</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -293,7 +296,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -302,16 +305,14 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -324,13 +325,12 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
@@ -350,12 +350,23 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="18">
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF3A10E6"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -544,16 +555,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF3A10E6"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -657,6 +658,43 @@
 </pivotCacheDefinition>
 </file>
 
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Andres R. Bucheli" refreshedDate="45516.875437615738" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="23" xr:uid="{3DEA46FE-55CA-4C56-BBD8-5521F3DBD117}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A5:E28" sheet="Exercise 1"/>
+  </cacheSource>
+  <cacheFields count="5">
+    <cacheField name="Country" numFmtId="0">
+      <sharedItems count="3">
+        <s v="Algeria"/>
+        <s v="Cyprus"/>
+        <s v="Tunisia"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Year" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1953" maxValue="1970"/>
+    </cacheField>
+    <cacheField name="Decade" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="50" maxValue="60" count="2">
+        <n v="50"/>
+        <n v="60"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Century" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="9" maxValue="9"/>
+    </cacheField>
+    <cacheField name="Book titles per capita" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="8.1199999999999992" maxValue="559.57000000000005"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="63">
   <r>
@@ -1098,13 +1136,248 @@
     <x v="8"/>
     <x v="1"/>
     <x v="0"/>
+    <n v="26.82"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="23">
+  <r>
+    <x v="0"/>
+    <n v="1953"/>
+    <x v="0"/>
+    <n v="9"/>
+    <n v="10.6"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="1954"/>
+    <x v="0"/>
+    <n v="9"/>
+    <n v="8.1199999999999992"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="1963"/>
+    <x v="1"/>
+    <n v="9"/>
+    <n v="12.6"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="1964"/>
+    <x v="1"/>
+    <n v="9"/>
+    <n v="13.61"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="1965"/>
+    <x v="1"/>
+    <n v="9"/>
+    <n v="10.95"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="1966"/>
+    <x v="1"/>
+    <n v="9"/>
+    <n v="15.88"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="1967"/>
+    <x v="1"/>
+    <n v="9"/>
+    <n v="20.22"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="1968"/>
+    <x v="1"/>
+    <n v="9"/>
+    <n v="21.98"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="1964"/>
+    <x v="1"/>
+    <n v="9"/>
+    <n v="289.86"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="1965"/>
+    <x v="1"/>
+    <n v="9"/>
+    <n v="140.49"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="1966"/>
+    <x v="1"/>
+    <n v="9"/>
+    <n v="265.55"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="1967"/>
+    <x v="1"/>
+    <n v="9"/>
+    <n v="345.35"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="1969"/>
+    <x v="1"/>
+    <n v="9"/>
+    <n v="559.57000000000005"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="1970"/>
+    <x v="1"/>
+    <n v="9"/>
+    <n v="333.55"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="1953"/>
+    <x v="0"/>
+    <n v="9"/>
+    <n v="15.08"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="1954"/>
+    <x v="0"/>
+    <n v="9"/>
+    <n v="23.81"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="1955"/>
+    <x v="0"/>
+    <n v="9"/>
+    <n v="32.24"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="1957"/>
+    <x v="0"/>
+    <n v="9"/>
+    <n v="29.11"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="1958"/>
+    <x v="0"/>
+    <n v="9"/>
+    <n v="24.46"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="1964"/>
+    <x v="1"/>
+    <n v="9"/>
+    <n v="23.95"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="1965"/>
+    <x v="1"/>
+    <n v="9"/>
+    <n v="43.8"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="1966"/>
+    <x v="1"/>
+    <n v="9"/>
+    <n v="53.46"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="1969"/>
+    <x v="1"/>
+    <n v="9"/>
     <n v="26.82"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4492BD4B-64E2-EB4F-B735-CACDF62C371D}" name="PivotTable5" cacheId="78" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{91CE70BB-24BA-4E17-97B2-DBD341B80081}" name="Сводная таблица3" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Значения" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="H3:K8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="2"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Среднее по полю Book titles per capita" fld="4" subtotal="average" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4492BD4B-64E2-EB4F-B735-CACDF62C371D}" name="PivotTable5" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="H3:K9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" showAll="0">
@@ -1228,9 +1501,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Стандартная">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1268,7 +1541,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Стандартная">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1374,7 +1647,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Стандартная">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1524,205 +1797,148 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{882B121D-80D9-D149-9ED0-C1047964B705}">
-  <dimension ref="B1:I24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="23" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:I23"/>
+  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="22.8"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="2"/>
-    <col min="2" max="2" width="10.83203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="129.1640625" style="2" customWidth="1"/>
-    <col min="4" max="5" width="10.83203125" style="2"/>
+    <col min="1" max="1" width="10.796875" style="2"/>
+    <col min="2" max="2" width="10.796875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="129.19921875" style="2" customWidth="1"/>
+    <col min="4" max="5" width="10.796875" style="2"/>
     <col min="6" max="6" width="39" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="10.83203125" style="2"/>
+    <col min="7" max="16384" width="10.796875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="2:9" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:9" s="1" customFormat="1" ht="15"/>
+    <row r="2" spans="2:9" s="1" customFormat="1" ht="30">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:9" s="1" customFormat="1" ht="25" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:9" s="1" customFormat="1" ht="24.6">
       <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="2:9" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2"/>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:9" s="1" customFormat="1" ht="15"/>
+    <row r="5" spans="2:9">
       <c r="B5" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:9">
       <c r="B6" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:9">
       <c r="B7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="7"/>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F7" s="6"/>
+    </row>
+    <row r="8" spans="2:9">
       <c r="B8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-    </row>
-    <row r="10" spans="2:9" ht="25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="2:9" ht="24.6">
       <c r="B10" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="8">
+    </row>
+    <row r="11" spans="2:9">
+      <c r="B11" s="7">
         <v>1</v>
       </c>
-      <c r="C11" s="24" t="str">
+      <c r="C11" s="21" t="str">
         <f>IF('Exercise 1'!A3&lt;&gt;"Correct!","Incomplete","Complete!")</f>
-        <v>Incomplete</v>
-      </c>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="24"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="24"/>
-      <c r="I11" s="24"/>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B12" s="6">
+        <v>Complete!</v>
+      </c>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="21"/>
+    </row>
+    <row r="12" spans="2:9">
+      <c r="B12" s="2">
         <v>2</v>
       </c>
       <c r="C12" s="2" t="str">
         <f>IF('Exercise 2'!A3&lt;&gt;"Correct!","Incomplete","Complete!")</f>
         <v>Incomplete</v>
       </c>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B13" s="6">
+    </row>
+    <row r="13" spans="2:9">
+      <c r="B13" s="2">
         <v>3</v>
       </c>
       <c r="C13" s="2" t="str">
         <f>IF('Exercise 3'!A3&lt;&gt;"Correct!","Incomplete","Complete!")</f>
         <v>Incomplete</v>
       </c>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B14" s="8">
+    </row>
+    <row r="14" spans="2:9">
+      <c r="B14" s="7">
         <v>4</v>
       </c>
       <c r="C14" s="5" t="str">
         <f>IF('Exercise 4'!A3&lt;&gt;"Correct!","Incomplete","Complete!")</f>
         <v>Incomplete</v>
       </c>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B16" s="23" t="s">
+    </row>
+    <row r="16" spans="2:9">
+      <c r="B16" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B17" s="8"/>
+    </row>
+    <row r="17" spans="2:3">
+      <c r="B17" s="7"/>
       <c r="C17" s="5"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B20" s="8"/>
+    </row>
+    <row r="20" spans="2:3">
+      <c r="B20" s="7"/>
       <c r="C20" s="5"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B23" s="8"/>
+    </row>
+    <row r="23" spans="2:3">
+      <c r="B23" s="7"/>
       <c r="C23" s="5"/>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B24" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="C11:I11"/>
   </mergeCells>
+  <conditionalFormatting sqref="C11">
+    <cfRule type="containsText" dxfId="17" priority="1" operator="containsText" text="Correct">
+      <formula>NOT(ISERROR(SEARCH("Correct",C11)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="16" priority="2" operator="containsText" text="Not quite">
+      <formula>NOT(ISERROR(SEARCH("Not quite",C11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C14 C17">
-    <cfRule type="containsText" dxfId="17" priority="18" operator="containsText" text="Not quite">
+    <cfRule type="containsText" dxfId="15" priority="17" operator="containsText" text="Correct">
+      <formula>NOT(ISERROR(SEARCH("Correct",C14)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="14" priority="18" operator="containsText" text="Not quite">
       <formula>NOT(ISERROR(SEARCH("Not quite",C14)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C14 C17">
-    <cfRule type="containsText" dxfId="16" priority="17" operator="containsText" text="Correct">
-      <formula>NOT(ISERROR(SEARCH("Correct",C14)))</formula>
+  <conditionalFormatting sqref="C20">
+    <cfRule type="containsText" dxfId="13" priority="5" operator="containsText" text="Correct">
+      <formula>NOT(ISERROR(SEARCH("Correct",C20)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C20">
-    <cfRule type="containsText" dxfId="15" priority="6" operator="containsText" text="Not quite">
+    <cfRule type="containsText" dxfId="12" priority="6" operator="containsText" text="Not quite">
       <formula>NOT(ISERROR(SEARCH("Not quite",C20)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20">
-    <cfRule type="containsText" dxfId="14" priority="5" operator="containsText" text="Correct">
-      <formula>NOT(ISERROR(SEARCH("Correct",C20)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C23">
-    <cfRule type="containsText" dxfId="13" priority="4" operator="containsText" text="Not quite">
-      <formula>NOT(ISERROR(SEARCH("Not quite",C23)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C23">
-    <cfRule type="containsText" dxfId="12" priority="3" operator="containsText" text="Correct">
+    <cfRule type="containsText" dxfId="11" priority="3" operator="containsText" text="Correct">
       <formula>NOT(ISERROR(SEARCH("Correct",C23)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C11">
-    <cfRule type="containsText" dxfId="11" priority="2" operator="containsText" text="Not quite">
-      <formula>NOT(ISERROR(SEARCH("Not quite",C11)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C11">
-    <cfRule type="containsText" dxfId="10" priority="1" operator="containsText" text="Correct">
-      <formula>NOT(ISERROR(SEARCH("Correct",C11)))</formula>
+    <cfRule type="containsText" dxfId="10" priority="4" operator="containsText" text="Not quite">
+      <formula>NOT(ISERROR(SEARCH("Not quite",C23)))</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
@@ -1735,62 +1951,71 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{871322B0-4E97-A249-9065-A631E1EF6A98}">
   <dimension ref="A1:K30"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="4" width="10.83203125" style="9"/>
-    <col min="5" max="5" width="18.6640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" style="9"/>
-    <col min="7" max="7" width="30.1640625" style="9" customWidth="1"/>
-    <col min="8" max="8" width="28.6640625" style="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.5" style="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="12.1640625" style="13" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="10.83203125" style="13"/>
+    <col min="1" max="4" width="10.796875" style="8"/>
+    <col min="5" max="5" width="18.69921875" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.796875" style="8"/>
+    <col min="7" max="7" width="30.19921875" style="8" customWidth="1"/>
+    <col min="8" max="8" width="35.3984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.09765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="11.8984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.19921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="10.796875" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="14" customFormat="1" ht="47" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:11" s="12" customFormat="1" ht="46.95" customHeight="1">
+      <c r="A1" s="10" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="9" customFormat="1" ht="103" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="25" t="s">
+    <row r="2" spans="1:11" s="8" customFormat="1" ht="103.05" customHeight="1">
+      <c r="A2" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="H2" s="12"/>
-    </row>
-    <row r="3" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="26" t="str" cm="1">
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="H2" s="10"/>
+    </row>
+    <row r="3" spans="1:11" ht="19.95" customHeight="1">
+      <c r="A3" s="23" t="str" cm="1">
         <f t="array" ref="A3">IF(ISBLANK(H3),"place the upper-left cell of your pivot table here --&gt;",IF(OR(SUMPRODUCT((I5:J7='Exercise 1 Checks'!A1:B3)-1)=0,SUMPRODUCT((I5:K6='Exercise 1 Checks'!D1:F2)-1)=0),"Correct!","Not quite! Did you remember to use an average instead of a sum?"))</f>
-        <v>place the upper-left cell of your pivot table here --&gt;</v>
-      </c>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3"/>
-      <c r="I3"/>
+        <v>Correct!</v>
+      </c>
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" s="13" t="s">
+        <v>29</v>
+      </c>
       <c r="J3"/>
       <c r="K3"/>
     </row>
-    <row r="4" spans="1:11" ht="20" x14ac:dyDescent="0.2">
-      <c r="A4" s="10"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="H4"/>
-      <c r="I4"/>
-      <c r="J4"/>
-      <c r="K4"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" ht="20.399999999999999">
+      <c r="A4" s="9"/>
+      <c r="H4" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4">
+        <v>50</v>
+      </c>
+      <c r="J4">
+        <v>60</v>
+      </c>
+      <c r="K4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1806,12 +2031,20 @@
       <c r="E5" t="s">
         <v>11</v>
       </c>
-      <c r="H5"/>
-      <c r="I5"/>
-      <c r="J5"/>
-      <c r="K5"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H5" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="26">
+        <v>9.36</v>
+      </c>
+      <c r="J5" s="26">
+        <v>15.873333333333333</v>
+      </c>
+      <c r="K5" s="26">
+        <v>14.244999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -1827,12 +2060,18 @@
       <c r="E6">
         <v>10.6</v>
       </c>
-      <c r="H6"/>
-      <c r="I6"/>
-      <c r="J6"/>
-      <c r="K6"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H6" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="26"/>
+      <c r="J6" s="26">
+        <v>322.39500000000004</v>
+      </c>
+      <c r="K6" s="26">
+        <v>322.39500000000004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -1848,12 +2087,20 @@
       <c r="E7">
         <v>8.1199999999999992</v>
       </c>
-      <c r="H7"/>
-      <c r="I7"/>
-      <c r="J7"/>
-      <c r="K7"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H7" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" s="26">
+        <v>24.939999999999998</v>
+      </c>
+      <c r="J7" s="26">
+        <v>37.0075</v>
+      </c>
+      <c r="K7" s="26">
+        <v>30.303333333333335</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -1869,12 +2116,20 @@
       <c r="E8">
         <v>12.6</v>
       </c>
-      <c r="H8"/>
-      <c r="I8"/>
-      <c r="J8"/>
-      <c r="K8"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H8" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8" s="26">
+        <v>20.488571428571426</v>
+      </c>
+      <c r="J8" s="26">
+        <v>136.10250000000005</v>
+      </c>
+      <c r="K8" s="26">
+        <v>100.91565217391305</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -1894,7 +2149,7 @@
       <c r="I9"/>
       <c r="J9"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1914,7 +2169,7 @@
       <c r="I10"/>
       <c r="J10"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -1934,7 +2189,7 @@
       <c r="I11"/>
       <c r="J11"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -1954,7 +2209,7 @@
       <c r="I12"/>
       <c r="J12"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -1974,7 +2229,7 @@
       <c r="I13"/>
       <c r="J13"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -1994,7 +2249,7 @@
       <c r="I14"/>
       <c r="J14"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -2014,7 +2269,7 @@
       <c r="I15"/>
       <c r="J15"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -2034,7 +2289,7 @@
       <c r="I16"/>
       <c r="J16"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -2054,7 +2309,7 @@
       <c r="I17"/>
       <c r="J17"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -2074,7 +2329,7 @@
       <c r="I18"/>
       <c r="J18"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>13</v>
       </c>
@@ -2094,7 +2349,7 @@
       <c r="I19"/>
       <c r="J19"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>14</v>
       </c>
@@ -2114,7 +2369,7 @@
       <c r="I20"/>
       <c r="J20"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -2131,7 +2386,7 @@
         <v>23.81</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>14</v>
       </c>
@@ -2148,7 +2403,7 @@
         <v>32.24</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>14</v>
       </c>
@@ -2165,7 +2420,7 @@
         <v>29.11</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>14</v>
       </c>
@@ -2182,7 +2437,7 @@
         <v>24.46</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
         <v>14</v>
       </c>
@@ -2199,7 +2454,7 @@
         <v>23.95</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
         <v>14</v>
       </c>
@@ -2216,7 +2471,7 @@
         <v>43.8</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
         <v>14</v>
       </c>
@@ -2233,7 +2488,7 @@
         <v>53.46</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>14</v>
       </c>
@@ -2250,20 +2505,18 @@
         <v>26.82</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="46" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="1:10" ht="46.05" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A3:G3"/>
   </mergeCells>
   <conditionalFormatting sqref="A3">
-    <cfRule type="containsText" dxfId="9" priority="2" operator="containsText" text="Not quite">
+    <cfRule type="containsText" dxfId="9" priority="1" operator="containsText" text="Correct">
+      <formula>NOT(ISERROR(SEARCH("Correct",A3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="8" priority="2" operator="containsText" text="Not quite">
       <formula>NOT(ISERROR(SEARCH("Not quite",A3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A3">
-    <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="Correct">
-      <formula>NOT(ISERROR(SEARCH("Correct",A3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2273,66 +2526,62 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF22AC83-BD6F-D84F-9592-454FFC20A7B9}">
   <dimension ref="A1:L32"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="4" width="10.83203125" style="9"/>
-    <col min="5" max="5" width="18.6640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" style="9"/>
-    <col min="7" max="7" width="32.33203125" style="9" customWidth="1"/>
-    <col min="8" max="8" width="13" style="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="25.33203125" style="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.1640625" style="13" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7" style="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.83203125" style="13" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="10.83203125" style="13"/>
+    <col min="1" max="4" width="10.796875" style="8"/>
+    <col min="5" max="5" width="18.69921875" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.796875" style="8"/>
+    <col min="7" max="7" width="32.296875" style="8" customWidth="1"/>
+    <col min="8" max="8" width="13" style="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.19921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7" style="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.796875" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="10.796875" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="14" customFormat="1" ht="47" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:12" s="12" customFormat="1" ht="46.95" customHeight="1">
+      <c r="A1" s="10" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="9" customFormat="1" ht="103" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="25" t="s">
+    <row r="2" spans="1:12" s="8" customFormat="1" ht="103.05" customHeight="1">
+      <c r="A2" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="H2" s="12"/>
-    </row>
-    <row r="3" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="26" t="str" cm="1">
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="H2" s="10"/>
+    </row>
+    <row r="3" spans="1:12" ht="19.95" customHeight="1">
+      <c r="A3" s="23" t="str" cm="1">
         <f t="array" ref="A3">IF(ISBLANK(I3),"place the upper-left cell of your pivot table here --&gt;",IF(OR(SUMPRODUCT((H4:I6='Exercise 2 checks'!A1:B3)-1)=0,SUMPRODUCT((I5:K5='Exercise 2 checks'!D2:F2)-1)=0),"Correct!","Not quite! Remember to use the maximum summary method."))</f>
         <v>place the upper-left cell of your pivot table here --&gt;</v>
       </c>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
       <c r="H3"/>
       <c r="I3"/>
       <c r="J3"/>
       <c r="K3"/>
       <c r="L3"/>
     </row>
-    <row r="4" spans="1:12" ht="20" x14ac:dyDescent="0.2">
-      <c r="A4" s="10"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
+    <row r="4" spans="1:12" ht="20.399999999999999">
+      <c r="A4" s="9"/>
       <c r="H4"/>
       <c r="I4"/>
       <c r="J4"/>
       <c r="K4"/>
       <c r="L4"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -2354,7 +2603,7 @@
       <c r="K5"/>
       <c r="L5"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -2375,7 +2624,7 @@
       <c r="J6"/>
       <c r="K6"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -2396,7 +2645,7 @@
       <c r="J7"/>
       <c r="K7"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -2417,7 +2666,7 @@
       <c r="J8"/>
       <c r="K8"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -2437,7 +2686,7 @@
       <c r="I9"/>
       <c r="J9"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -2457,7 +2706,7 @@
       <c r="I10"/>
       <c r="J10"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -2477,7 +2726,7 @@
       <c r="I11"/>
       <c r="J11"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -2497,7 +2746,7 @@
       <c r="I12"/>
       <c r="J12"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -2517,7 +2766,7 @@
       <c r="I13"/>
       <c r="J13"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -2537,7 +2786,7 @@
       <c r="I14"/>
       <c r="J14"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -2557,7 +2806,7 @@
       <c r="I15"/>
       <c r="J15"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -2577,7 +2826,7 @@
       <c r="I16"/>
       <c r="J16"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -2597,7 +2846,7 @@
       <c r="I17"/>
       <c r="J17"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -2617,7 +2866,7 @@
       <c r="I18"/>
       <c r="J18"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>13</v>
       </c>
@@ -2637,7 +2886,7 @@
       <c r="I19"/>
       <c r="J19"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>14</v>
       </c>
@@ -2657,7 +2906,7 @@
       <c r="I20"/>
       <c r="J20"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -2674,7 +2923,7 @@
         <v>23.81</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>14</v>
       </c>
@@ -2691,7 +2940,7 @@
         <v>32.24</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>14</v>
       </c>
@@ -2708,7 +2957,7 @@
         <v>29.11</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>14</v>
       </c>
@@ -2725,7 +2974,7 @@
         <v>24.46</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
         <v>14</v>
       </c>
@@ -2742,7 +2991,7 @@
         <v>23.95</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
         <v>14</v>
       </c>
@@ -2759,7 +3008,7 @@
         <v>43.8</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
         <v>14</v>
       </c>
@@ -2776,7 +3025,7 @@
         <v>53.46</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>14</v>
       </c>
@@ -2793,21 +3042,20 @@
         <v>26.82</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="41" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="25"/>
-      <c r="B31" s="25"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="25"/>
-      <c r="F31" s="25"/>
-    </row>
-    <row r="32" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="11"/>
-      <c r="C32" s="27"/>
-      <c r="D32" s="27"/>
-      <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="27"/>
+    <row r="31" spans="1:10" ht="40.950000000000003" customHeight="1">
+      <c r="A31" s="22"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+    </row>
+    <row r="32" spans="1:10" ht="45" customHeight="1">
+      <c r="C32" s="24"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2817,23 +3065,19 @@
     <mergeCell ref="C32:G32"/>
   </mergeCells>
   <conditionalFormatting sqref="A3">
-    <cfRule type="containsText" dxfId="7" priority="4" operator="containsText" text="Not quite">
+    <cfRule type="containsText" dxfId="7" priority="3" operator="containsText" text="Correct">
+      <formula>NOT(ISERROR(SEARCH("Correct",A3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="6" priority="4" operator="containsText" text="Not quite">
       <formula>NOT(ISERROR(SEARCH("Not quite",A3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A3">
-    <cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="Correct">
-      <formula>NOT(ISERROR(SEARCH("Correct",A3)))</formula>
+  <conditionalFormatting sqref="C32">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="Correct">
+      <formula>NOT(ISERROR(SEARCH("Correct",C32)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C32">
-    <cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="Not quite">
+    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="Not quite">
       <formula>NOT(ISERROR(SEARCH("Not quite",C32)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C32">
-    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="Correct">
-      <formula>NOT(ISERROR(SEARCH("Correct",C32)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2846,52 +3090,52 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBD3880F-FB99-464C-902C-D72ECF3F02EF}">
   <dimension ref="A1:R68"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="4" width="10.83203125" style="9"/>
-    <col min="5" max="5" width="18.6640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" style="9"/>
-    <col min="7" max="7" width="30.1640625" style="9" customWidth="1"/>
-    <col min="8" max="8" width="13" style="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.5" style="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.6640625" style="13" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.1640625" style="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7" style="13" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.83203125" style="13" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.6640625" style="13" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.1640625" style="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7" style="13" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.83203125" style="13" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="10.83203125" style="13"/>
+    <col min="1" max="4" width="10.796875" style="8"/>
+    <col min="5" max="5" width="18.69921875" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.796875" style="8"/>
+    <col min="7" max="7" width="30.19921875" style="8" customWidth="1"/>
+    <col min="8" max="8" width="13" style="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.69921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.19921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.796875" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.69921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.19921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7" style="11" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.796875" style="11" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="10.796875" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="14" customFormat="1" ht="47" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:18" s="12" customFormat="1" ht="46.95" customHeight="1">
+      <c r="A1" s="10" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:18" s="9" customFormat="1" ht="103" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="25" t="s">
+    <row r="2" spans="1:18" s="8" customFormat="1" ht="103.05" customHeight="1">
+      <c r="A2" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="H2" s="12"/>
-    </row>
-    <row r="3" spans="1:18" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="26" t="str" cm="1">
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="H2" s="10"/>
+    </row>
+    <row r="3" spans="1:18" ht="19.95" customHeight="1">
+      <c r="A3" s="23" t="str" cm="1">
         <f t="array" ref="A3">IF(ISBLANK(H3),"place the upper-left cell of your pivot table here --&gt;",IF(OR(SUMPRODUCT((I5:J8='Exercise 3 checks'!A1:B4)-1)=0,SUMPRODUCT((I5:L6='Exercise 3 checks'!D1:G2)-1)=0),"Correct!","Not quite! Did you use 'Year' as the values with the 'Count' option?"))</f>
         <v>place the upper-left cell of your pivot table here --&gt;</v>
       </c>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
       <c r="H3"/>
       <c r="I3"/>
       <c r="J3"/>
@@ -2904,12 +3148,8 @@
       <c r="Q3"/>
       <c r="R3"/>
     </row>
-    <row r="4" spans="1:18" ht="20" x14ac:dyDescent="0.2">
-      <c r="A4" s="10"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
+    <row r="4" spans="1:18" ht="20.399999999999999">
+      <c r="A4" s="9"/>
       <c r="H4"/>
       <c r="I4"/>
       <c r="J4"/>
@@ -2922,7 +3162,7 @@
       <c r="Q4"/>
       <c r="R4"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -2950,7 +3190,7 @@
       <c r="Q5"/>
       <c r="R5"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -2978,7 +3218,7 @@
       <c r="Q6"/>
       <c r="R6"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -3001,7 +3241,7 @@
       <c r="L7"/>
       <c r="M7"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -3022,7 +3262,7 @@
       <c r="J8"/>
       <c r="K8"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -3043,7 +3283,7 @@
       <c r="J9"/>
       <c r="K9"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -3064,7 +3304,7 @@
       <c r="J10"/>
       <c r="K10"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -3085,7 +3325,7 @@
       <c r="J11"/>
       <c r="K11"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -3106,7 +3346,7 @@
       <c r="J12"/>
       <c r="K12"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -3127,7 +3367,7 @@
       <c r="J13"/>
       <c r="K13"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -3148,7 +3388,7 @@
       <c r="J14"/>
       <c r="K14"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -3169,7 +3409,7 @@
       <c r="J15"/>
       <c r="K15"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -3190,7 +3430,7 @@
       <c r="J16"/>
       <c r="K16"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -3211,7 +3451,7 @@
       <c r="J17"/>
       <c r="K17"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -3232,7 +3472,7 @@
       <c r="J18"/>
       <c r="K18"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11">
       <c r="A19" t="s">
         <v>13</v>
       </c>
@@ -3253,7 +3493,7 @@
       <c r="J19"/>
       <c r="K19"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -3274,7 +3514,7 @@
       <c r="J20"/>
       <c r="K20"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -3295,7 +3535,7 @@
       <c r="J21"/>
       <c r="K21"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11">
       <c r="A22" t="s">
         <v>19</v>
       </c>
@@ -3316,7 +3556,7 @@
       <c r="J22"/>
       <c r="K22"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11">
       <c r="A23" t="s">
         <v>19</v>
       </c>
@@ -3337,7 +3577,7 @@
       <c r="J23"/>
       <c r="K23"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11">
       <c r="A24" t="s">
         <v>19</v>
       </c>
@@ -3358,7 +3598,7 @@
       <c r="J24"/>
       <c r="K24"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11">
       <c r="A25" t="s">
         <v>19</v>
       </c>
@@ -3379,7 +3619,7 @@
       <c r="J25"/>
       <c r="K25"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11">
       <c r="A26" t="s">
         <v>19</v>
       </c>
@@ -3400,7 +3640,7 @@
       <c r="J26"/>
       <c r="K26"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11">
       <c r="A27" t="s">
         <v>19</v>
       </c>
@@ -3421,7 +3661,7 @@
       <c r="J27"/>
       <c r="K27"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11">
       <c r="A28" t="s">
         <v>19</v>
       </c>
@@ -3442,7 +3682,7 @@
       <c r="J28"/>
       <c r="K28"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11">
       <c r="A29" t="s">
         <v>19</v>
       </c>
@@ -3463,7 +3703,7 @@
       <c r="J29"/>
       <c r="K29"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11">
       <c r="A30" t="s">
         <v>19</v>
       </c>
@@ -3484,7 +3724,7 @@
       <c r="J30"/>
       <c r="K30"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11">
       <c r="A31" t="s">
         <v>19</v>
       </c>
@@ -3505,7 +3745,7 @@
       <c r="J31"/>
       <c r="K31"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11">
       <c r="A32" t="s">
         <v>19</v>
       </c>
@@ -3526,7 +3766,7 @@
       <c r="J32"/>
       <c r="K32"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11">
       <c r="A33" t="s">
         <v>19</v>
       </c>
@@ -3547,7 +3787,7 @@
       <c r="J33"/>
       <c r="K33"/>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11">
       <c r="A34" t="s">
         <v>19</v>
       </c>
@@ -3568,7 +3808,7 @@
       <c r="J34"/>
       <c r="K34"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11">
       <c r="A35" t="s">
         <v>19</v>
       </c>
@@ -3589,7 +3829,7 @@
       <c r="J35"/>
       <c r="K35"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11">
       <c r="A36" t="s">
         <v>19</v>
       </c>
@@ -3610,7 +3850,7 @@
       <c r="J36"/>
       <c r="K36"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11">
       <c r="A37" t="s">
         <v>19</v>
       </c>
@@ -3631,7 +3871,7 @@
       <c r="J37"/>
       <c r="K37"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11">
       <c r="A38" t="s">
         <v>19</v>
       </c>
@@ -3652,7 +3892,7 @@
       <c r="J38"/>
       <c r="K38"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11">
       <c r="A39" t="s">
         <v>19</v>
       </c>
@@ -3673,7 +3913,7 @@
       <c r="J39"/>
       <c r="K39"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11">
       <c r="A40" t="s">
         <v>19</v>
       </c>
@@ -3694,7 +3934,7 @@
       <c r="J40"/>
       <c r="K40"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11">
       <c r="A41" t="s">
         <v>19</v>
       </c>
@@ -3715,7 +3955,7 @@
       <c r="J41"/>
       <c r="K41"/>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11">
       <c r="A42" t="s">
         <v>19</v>
       </c>
@@ -3736,7 +3976,7 @@
       <c r="J42"/>
       <c r="K42"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11">
       <c r="A43" t="s">
         <v>19</v>
       </c>
@@ -3757,7 +3997,7 @@
       <c r="J43"/>
       <c r="K43"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11">
       <c r="A44" t="s">
         <v>19</v>
       </c>
@@ -3778,7 +4018,7 @@
       <c r="J44"/>
       <c r="K44"/>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11">
       <c r="A45" t="s">
         <v>19</v>
       </c>
@@ -3799,7 +4039,7 @@
       <c r="J45"/>
       <c r="K45"/>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11">
       <c r="A46" t="s">
         <v>19</v>
       </c>
@@ -3820,7 +4060,7 @@
       <c r="J46"/>
       <c r="K46"/>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11">
       <c r="A47" t="s">
         <v>19</v>
       </c>
@@ -3837,7 +4077,7 @@
         <v>41.71</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11">
       <c r="A48" t="s">
         <v>19</v>
       </c>
@@ -3854,7 +4094,7 @@
         <v>28.12</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5">
       <c r="A49" t="s">
         <v>19</v>
       </c>
@@ -3871,7 +4111,7 @@
         <v>24.75</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5">
       <c r="A50" t="s">
         <v>19</v>
       </c>
@@ -3888,7 +4128,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5">
       <c r="A51" t="s">
         <v>19</v>
       </c>
@@ -3905,7 +4145,7 @@
         <v>24.42</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5">
       <c r="A52" t="s">
         <v>19</v>
       </c>
@@ -3922,7 +4162,7 @@
         <v>39.299999999999997</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5">
       <c r="A53" t="s">
         <v>19</v>
       </c>
@@ -3939,7 +4179,7 @@
         <v>27.7</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5">
       <c r="A54" t="s">
         <v>19</v>
       </c>
@@ -3956,7 +4196,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:5">
       <c r="A55" t="s">
         <v>19</v>
       </c>
@@ -3973,7 +4213,7 @@
         <v>24.49</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:5">
       <c r="A56" t="s">
         <v>19</v>
       </c>
@@ -3990,7 +4230,7 @@
         <v>20.98</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5">
       <c r="A57" t="s">
         <v>19</v>
       </c>
@@ -4007,7 +4247,7 @@
         <v>22.03</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5">
       <c r="A58" t="s">
         <v>19</v>
       </c>
@@ -4024,7 +4264,7 @@
         <v>25.96</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5">
       <c r="A59" t="s">
         <v>19</v>
       </c>
@@ -4041,7 +4281,7 @@
         <v>26.15</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5">
       <c r="A60" t="s">
         <v>14</v>
       </c>
@@ -4058,7 +4298,7 @@
         <v>15.08</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5">
       <c r="A61" t="s">
         <v>14</v>
       </c>
@@ -4075,7 +4315,7 @@
         <v>23.81</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5">
       <c r="A62" t="s">
         <v>14</v>
       </c>
@@ -4092,7 +4332,7 @@
         <v>32.24</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5">
       <c r="A63" t="s">
         <v>14</v>
       </c>
@@ -4109,7 +4349,7 @@
         <v>29.11</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5">
       <c r="A64" t="s">
         <v>14</v>
       </c>
@@ -4126,7 +4366,7 @@
         <v>24.46</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5">
       <c r="A65" t="s">
         <v>14</v>
       </c>
@@ -4143,7 +4383,7 @@
         <v>23.95</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:5">
       <c r="A66" t="s">
         <v>14</v>
       </c>
@@ -4160,7 +4400,7 @@
         <v>43.8</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:5">
       <c r="A67" t="s">
         <v>14</v>
       </c>
@@ -4177,7 +4417,7 @@
         <v>53.46</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:5">
       <c r="A68" t="s">
         <v>14</v>
       </c>
@@ -4200,13 +4440,11 @@
     <mergeCell ref="A3:G3"/>
   </mergeCells>
   <conditionalFormatting sqref="A3">
-    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="Not quite">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="Correct">
+      <formula>NOT(ISERROR(SEARCH("Correct",A3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="Not quite">
       <formula>NOT(ISERROR(SEARCH("Not quite",A3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A3">
-    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="Correct">
-      <formula>NOT(ISERROR(SEARCH("Correct",A3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4216,56 +4454,56 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C63D4939-7824-8342-92E5-A902EA109E8C}">
   <dimension ref="A1:R68"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="4" width="10.83203125" style="9"/>
-    <col min="5" max="5" width="18.6640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" style="9"/>
-    <col min="7" max="7" width="45.33203125" style="9" customWidth="1"/>
-    <col min="8" max="8" width="13" style="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.5" style="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3.1640625" style="13" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.83203125" style="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.33203125" style="13" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.1640625" style="13" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.83203125" style="13" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.83203125" style="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7" style="13" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.83203125" style="13" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="10.83203125" style="13"/>
+    <col min="1" max="4" width="10.796875" style="8"/>
+    <col min="5" max="5" width="18.69921875" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.796875" style="8"/>
+    <col min="7" max="7" width="45.296875" style="8" customWidth="1"/>
+    <col min="8" max="8" width="13" style="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3.19921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.796875" style="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="3.19921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.796875" style="11" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.796875" style="11" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7" style="11" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.796875" style="11" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="10.796875" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="14" customFormat="1" ht="47" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:18" s="12" customFormat="1" ht="46.95" customHeight="1">
+      <c r="A1" s="10" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:18" s="9" customFormat="1" ht="185" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="28" t="s">
+    <row r="2" spans="1:18" s="8" customFormat="1" ht="184.95" customHeight="1">
+      <c r="A2" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="H2" s="12"/>
-    </row>
-    <row r="3" spans="1:18" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="26" t="str" cm="1">
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="H2" s="10"/>
+    </row>
+    <row r="3" spans="1:18" ht="19.95" customHeight="1">
+      <c r="A3" s="23" t="str" cm="1">
         <f t="array" ref="A3">IF(SUMPRODUCT((H5:K8='Exercise 4 checks'!A1:D4)-1)=0,"add 'century' to the columns --&gt;",IF(OR(SUMPRODUCT((H6:O9='Exercise 4 checks'!F1:M4)-1)=0,SUMPRODUCT((H6:O9='Exercise 4 checks'!O1:V4)-1)=0),"Correct!","Not quite! The only change you should make is adding 'Century' to the 'Columns'"))</f>
         <v>add 'century' to the columns --&gt;</v>
       </c>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="15" t="s">
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="15" t="s">
+      <c r="I3" s="13" t="s">
         <v>17</v>
       </c>
       <c r="J3"/>
@@ -4278,13 +4516,9 @@
       <c r="Q3"/>
       <c r="R3"/>
     </row>
-    <row r="4" spans="1:18" ht="20" x14ac:dyDescent="0.2">
-      <c r="A4" s="10"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="H4" s="15" t="s">
+    <row r="4" spans="1:18" ht="20.399999999999999">
+      <c r="A4" s="9"/>
+      <c r="H4" s="13" t="s">
         <v>15</v>
       </c>
       <c r="I4">
@@ -4304,7 +4538,7 @@
       <c r="Q4"/>
       <c r="R4"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -4320,16 +4554,16 @@
       <c r="E5" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="16" t="s">
+      <c r="H5" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="18">
+      <c r="I5">
         <v>2</v>
       </c>
-      <c r="J5" s="18">
+      <c r="J5">
         <v>6</v>
       </c>
-      <c r="K5" s="18">
+      <c r="K5">
         <v>8</v>
       </c>
       <c r="L5"/>
@@ -4340,7 +4574,7 @@
       <c r="Q5"/>
       <c r="R5"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -4356,14 +4590,14 @@
       <c r="E6">
         <v>10.6</v>
       </c>
-      <c r="H6" s="16" t="s">
+      <c r="H6" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18">
+      <c r="I6"/>
+      <c r="J6">
         <v>6</v>
       </c>
-      <c r="K6" s="18">
+      <c r="K6">
         <v>6</v>
       </c>
       <c r="L6"/>
@@ -4374,7 +4608,7 @@
       <c r="Q6"/>
       <c r="R6"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -4390,16 +4624,16 @@
       <c r="E7">
         <v>8.1199999999999992</v>
       </c>
-      <c r="H7" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="I7" s="18">
+      <c r="H7" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7">
         <v>18</v>
       </c>
-      <c r="J7" s="18">
+      <c r="J7">
         <v>22</v>
       </c>
-      <c r="K7" s="18">
+      <c r="K7">
         <v>40</v>
       </c>
       <c r="L7"/>
@@ -4407,7 +4641,7 @@
       <c r="N7"/>
       <c r="O7"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -4423,16 +4657,16 @@
       <c r="E8">
         <v>12.6</v>
       </c>
-      <c r="H8" s="16" t="s">
+      <c r="H8" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="I8" s="18">
+      <c r="I8">
         <v>5</v>
       </c>
-      <c r="J8" s="18">
+      <c r="J8">
         <v>4</v>
       </c>
-      <c r="K8" s="18">
+      <c r="K8">
         <v>9</v>
       </c>
       <c r="L8"/>
@@ -4440,7 +4674,7 @@
       <c r="N8"/>
       <c r="O8"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -4456,16 +4690,16 @@
       <c r="E9">
         <v>13.61</v>
       </c>
-      <c r="H9" s="16" t="s">
+      <c r="H9" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="I9" s="18">
+      <c r="I9">
         <v>25</v>
       </c>
-      <c r="J9" s="18">
+      <c r="J9">
         <v>38</v>
       </c>
-      <c r="K9" s="18">
+      <c r="K9">
         <v>63</v>
       </c>
       <c r="L9"/>
@@ -4473,7 +4707,7 @@
       <c r="N9"/>
       <c r="O9"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -4498,7 +4732,7 @@
       <c r="N10"/>
       <c r="O10"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -4519,7 +4753,7 @@
       <c r="J11"/>
       <c r="K11"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -4540,7 +4774,7 @@
       <c r="J12"/>
       <c r="K12"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -4561,7 +4795,7 @@
       <c r="J13"/>
       <c r="K13"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -4582,7 +4816,7 @@
       <c r="J14"/>
       <c r="K14"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -4603,7 +4837,7 @@
       <c r="J15"/>
       <c r="K15"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -4624,7 +4858,7 @@
       <c r="J16"/>
       <c r="K16"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -4645,7 +4879,7 @@
       <c r="J17"/>
       <c r="K17"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -4666,7 +4900,7 @@
       <c r="J18"/>
       <c r="K18"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11">
       <c r="A19" t="s">
         <v>13</v>
       </c>
@@ -4687,7 +4921,7 @@
       <c r="J19"/>
       <c r="K19"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -4708,7 +4942,7 @@
       <c r="J20"/>
       <c r="K20"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -4729,7 +4963,7 @@
       <c r="J21"/>
       <c r="K21"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11">
       <c r="A22" t="s">
         <v>19</v>
       </c>
@@ -4750,7 +4984,7 @@
       <c r="J22"/>
       <c r="K22"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11">
       <c r="A23" t="s">
         <v>19</v>
       </c>
@@ -4771,7 +5005,7 @@
       <c r="J23"/>
       <c r="K23"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11">
       <c r="A24" t="s">
         <v>19</v>
       </c>
@@ -4792,7 +5026,7 @@
       <c r="J24"/>
       <c r="K24"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11">
       <c r="A25" t="s">
         <v>19</v>
       </c>
@@ -4813,7 +5047,7 @@
       <c r="J25"/>
       <c r="K25"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11">
       <c r="A26" t="s">
         <v>19</v>
       </c>
@@ -4834,7 +5068,7 @@
       <c r="J26"/>
       <c r="K26"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11">
       <c r="A27" t="s">
         <v>19</v>
       </c>
@@ -4855,7 +5089,7 @@
       <c r="J27"/>
       <c r="K27"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11">
       <c r="A28" t="s">
         <v>19</v>
       </c>
@@ -4876,7 +5110,7 @@
       <c r="J28"/>
       <c r="K28"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11">
       <c r="A29" t="s">
         <v>19</v>
       </c>
@@ -4897,7 +5131,7 @@
       <c r="J29"/>
       <c r="K29"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11">
       <c r="A30" t="s">
         <v>19</v>
       </c>
@@ -4918,7 +5152,7 @@
       <c r="J30"/>
       <c r="K30"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11">
       <c r="A31" t="s">
         <v>19</v>
       </c>
@@ -4939,7 +5173,7 @@
       <c r="J31"/>
       <c r="K31"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11">
       <c r="A32" t="s">
         <v>19</v>
       </c>
@@ -4960,7 +5194,7 @@
       <c r="J32"/>
       <c r="K32"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11">
       <c r="A33" t="s">
         <v>19</v>
       </c>
@@ -4981,7 +5215,7 @@
       <c r="J33"/>
       <c r="K33"/>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11">
       <c r="A34" t="s">
         <v>19</v>
       </c>
@@ -5002,7 +5236,7 @@
       <c r="J34"/>
       <c r="K34"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11">
       <c r="A35" t="s">
         <v>19</v>
       </c>
@@ -5023,7 +5257,7 @@
       <c r="J35"/>
       <c r="K35"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11">
       <c r="A36" t="s">
         <v>19</v>
       </c>
@@ -5044,7 +5278,7 @@
       <c r="J36"/>
       <c r="K36"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11">
       <c r="A37" t="s">
         <v>19</v>
       </c>
@@ -5065,7 +5299,7 @@
       <c r="J37"/>
       <c r="K37"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11">
       <c r="A38" t="s">
         <v>19</v>
       </c>
@@ -5086,7 +5320,7 @@
       <c r="J38"/>
       <c r="K38"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11">
       <c r="A39" t="s">
         <v>19</v>
       </c>
@@ -5107,7 +5341,7 @@
       <c r="J39"/>
       <c r="K39"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11">
       <c r="A40" t="s">
         <v>19</v>
       </c>
@@ -5128,7 +5362,7 @@
       <c r="J40"/>
       <c r="K40"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11">
       <c r="A41" t="s">
         <v>19</v>
       </c>
@@ -5149,7 +5383,7 @@
       <c r="J41"/>
       <c r="K41"/>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11">
       <c r="A42" t="s">
         <v>19</v>
       </c>
@@ -5170,7 +5404,7 @@
       <c r="J42"/>
       <c r="K42"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11">
       <c r="A43" t="s">
         <v>19</v>
       </c>
@@ -5191,7 +5425,7 @@
       <c r="J43"/>
       <c r="K43"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11">
       <c r="A44" t="s">
         <v>19</v>
       </c>
@@ -5212,7 +5446,7 @@
       <c r="J44"/>
       <c r="K44"/>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11">
       <c r="A45" t="s">
         <v>19</v>
       </c>
@@ -5233,7 +5467,7 @@
       <c r="J45"/>
       <c r="K45"/>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11">
       <c r="A46" t="s">
         <v>19</v>
       </c>
@@ -5254,7 +5488,7 @@
       <c r="J46"/>
       <c r="K46"/>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11">
       <c r="A47" t="s">
         <v>19</v>
       </c>
@@ -5271,7 +5505,7 @@
         <v>41.71</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11">
       <c r="A48" t="s">
         <v>19</v>
       </c>
@@ -5288,7 +5522,7 @@
         <v>28.12</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5">
       <c r="A49" t="s">
         <v>19</v>
       </c>
@@ -5305,7 +5539,7 @@
         <v>24.75</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5">
       <c r="A50" t="s">
         <v>19</v>
       </c>
@@ -5322,7 +5556,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5">
       <c r="A51" t="s">
         <v>19</v>
       </c>
@@ -5339,7 +5573,7 @@
         <v>24.42</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5">
       <c r="A52" t="s">
         <v>19</v>
       </c>
@@ -5356,7 +5590,7 @@
         <v>39.299999999999997</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5">
       <c r="A53" t="s">
         <v>19</v>
       </c>
@@ -5373,7 +5607,7 @@
         <v>27.7</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5">
       <c r="A54" t="s">
         <v>19</v>
       </c>
@@ -5390,7 +5624,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:5">
       <c r="A55" t="s">
         <v>19</v>
       </c>
@@ -5407,7 +5641,7 @@
         <v>24.49</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:5">
       <c r="A56" t="s">
         <v>19</v>
       </c>
@@ -5424,7 +5658,7 @@
         <v>20.98</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5">
       <c r="A57" t="s">
         <v>19</v>
       </c>
@@ -5441,7 +5675,7 @@
         <v>22.03</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5">
       <c r="A58" t="s">
         <v>19</v>
       </c>
@@ -5458,7 +5692,7 @@
         <v>25.96</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5">
       <c r="A59" t="s">
         <v>19</v>
       </c>
@@ -5475,7 +5709,7 @@
         <v>26.15</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5">
       <c r="A60" t="s">
         <v>14</v>
       </c>
@@ -5492,7 +5726,7 @@
         <v>15.08</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5">
       <c r="A61" t="s">
         <v>14</v>
       </c>
@@ -5509,7 +5743,7 @@
         <v>23.81</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5">
       <c r="A62" t="s">
         <v>14</v>
       </c>
@@ -5526,7 +5760,7 @@
         <v>32.24</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5">
       <c r="A63" t="s">
         <v>14</v>
       </c>
@@ -5543,7 +5777,7 @@
         <v>29.11</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5">
       <c r="A64" t="s">
         <v>14</v>
       </c>
@@ -5560,7 +5794,7 @@
         <v>24.46</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5">
       <c r="A65" t="s">
         <v>14</v>
       </c>
@@ -5577,7 +5811,7 @@
         <v>23.95</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:5">
       <c r="A66" t="s">
         <v>14</v>
       </c>
@@ -5594,7 +5828,7 @@
         <v>43.8</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:5">
       <c r="A67" t="s">
         <v>14</v>
       </c>
@@ -5611,7 +5845,7 @@
         <v>53.46</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:5">
       <c r="A68" t="s">
         <v>14</v>
       </c>
@@ -5634,13 +5868,11 @@
     <mergeCell ref="A3:G3"/>
   </mergeCells>
   <conditionalFormatting sqref="A3">
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Not quite">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="Correct">
+      <formula>NOT(ISERROR(SEARCH("Correct",A3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="Not quite">
       <formula>NOT(ISERROR(SEARCH("Not quite",A3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A3">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Correct">
-      <formula>NOT(ISERROR(SEARCH("Correct",A3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5650,215 +5882,201 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62858130-AEF8-5C4F-9BD1-FA281554AB5A}">
   <dimension ref="A1:V4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6"/>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:22">
+      <c r="A1" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="20">
+      <c r="B1" s="17">
         <v>2</v>
       </c>
-      <c r="C1" s="20">
+      <c r="C1" s="17">
         <v>6</v>
       </c>
-      <c r="D1" s="20">
+      <c r="D1" s="17">
         <v>8</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18">
+      <c r="H1">
         <v>2</v>
       </c>
-      <c r="I1" s="21">
+      <c r="I1" s="18">
         <v>2</v>
       </c>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18">
+      <c r="K1">
         <v>6</v>
       </c>
-      <c r="L1" s="21">
+      <c r="L1" s="18">
         <v>6</v>
       </c>
-      <c r="M1" s="18">
+      <c r="M1">
         <v>8</v>
       </c>
-      <c r="O1" s="16" t="s">
+      <c r="O1" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="18"/>
-      <c r="Q1" s="18"/>
-      <c r="R1" s="21"/>
-      <c r="S1" s="18">
+      <c r="R1" s="18"/>
+      <c r="S1">
         <v>2</v>
       </c>
-      <c r="T1" s="18">
+      <c r="T1">
         <v>6</v>
       </c>
-      <c r="U1" s="21">
+      <c r="U1" s="18">
         <v>8</v>
       </c>
-      <c r="V1" s="18">
+      <c r="V1">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A2" s="19" t="s">
+    <row r="2" spans="1:22">
+      <c r="A2" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20">
+      <c r="B2" s="17"/>
+      <c r="C2" s="17">
         <v>6</v>
       </c>
-      <c r="D2" s="20">
+      <c r="D2" s="17">
         <v>6</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="F2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18">
+      <c r="I2" s="18"/>
+      <c r="K2">
         <v>6</v>
       </c>
-      <c r="L2" s="21">
+      <c r="L2" s="18">
         <v>6</v>
       </c>
-      <c r="M2" s="18">
+      <c r="M2">
         <v>6</v>
       </c>
-      <c r="O2" s="16" t="s">
+      <c r="O2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="P2" s="18"/>
-      <c r="Q2" s="18"/>
-      <c r="R2" s="21"/>
-      <c r="S2" s="18"/>
-      <c r="T2" s="18">
+      <c r="R2" s="18"/>
+      <c r="T2">
         <v>6</v>
       </c>
-      <c r="U2" s="21">
+      <c r="U2" s="18">
         <v>6</v>
       </c>
-      <c r="V2" s="18">
+      <c r="V2">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A3" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="20">
+    <row r="3" spans="1:22">
+      <c r="A3" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="17">
         <v>18</v>
       </c>
-      <c r="C3" s="20">
+      <c r="C3" s="17">
         <v>22</v>
       </c>
-      <c r="D3" s="20">
+      <c r="D3" s="17">
         <v>40</v>
       </c>
-      <c r="F3" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="18">
+      <c r="F3" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3">
         <v>10</v>
       </c>
-      <c r="H3" s="18">
+      <c r="H3">
         <v>8</v>
       </c>
-      <c r="I3" s="21">
+      <c r="I3" s="18">
         <v>18</v>
       </c>
-      <c r="J3" s="18">
+      <c r="J3">
         <v>11</v>
       </c>
-      <c r="K3" s="18">
+      <c r="K3">
         <v>11</v>
       </c>
-      <c r="L3" s="21">
+      <c r="L3" s="18">
         <v>22</v>
       </c>
-      <c r="M3" s="18">
+      <c r="M3">
         <v>40</v>
       </c>
-      <c r="O3" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="P3" s="18">
+      <c r="O3" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="P3">
         <v>10</v>
       </c>
-      <c r="Q3" s="18">
+      <c r="Q3">
         <v>11</v>
       </c>
-      <c r="R3" s="21">
+      <c r="R3" s="18">
         <v>21</v>
       </c>
-      <c r="S3" s="18">
+      <c r="S3">
         <v>8</v>
       </c>
-      <c r="T3" s="18">
+      <c r="T3">
         <v>11</v>
       </c>
-      <c r="U3" s="21">
-        <v>19</v>
-      </c>
-      <c r="V3" s="18">
+      <c r="U3" s="18">
+        <v>19</v>
+      </c>
+      <c r="V3">
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A4" s="19" t="s">
+    <row r="4" spans="1:22">
+      <c r="A4" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="20">
+      <c r="B4" s="17">
         <v>5</v>
       </c>
-      <c r="C4" s="20">
+      <c r="C4" s="17">
         <v>4</v>
       </c>
-      <c r="D4" s="20">
-        <v>9</v>
-      </c>
-      <c r="F4" s="16" t="s">
+      <c r="D4" s="17">
+        <v>9</v>
+      </c>
+      <c r="F4" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18">
+      <c r="H4">
         <v>5</v>
       </c>
-      <c r="I4" s="21">
+      <c r="I4" s="18">
         <v>5</v>
       </c>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18">
+      <c r="K4">
         <v>4</v>
       </c>
-      <c r="L4" s="21">
+      <c r="L4" s="18">
         <v>4</v>
       </c>
-      <c r="M4" s="18">
-        <v>9</v>
-      </c>
-      <c r="O4" s="16" t="s">
+      <c r="M4">
+        <v>9</v>
+      </c>
+      <c r="O4" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="P4" s="18"/>
-      <c r="Q4" s="18"/>
-      <c r="R4" s="21"/>
-      <c r="S4" s="18">
+      <c r="R4" s="18"/>
+      <c r="S4">
         <v>5</v>
       </c>
-      <c r="T4" s="18">
+      <c r="T4">
         <v>4</v>
       </c>
-      <c r="U4" s="21">
-        <v>9</v>
-      </c>
-      <c r="V4" s="18">
+      <c r="U4" s="18">
+        <v>9</v>
+      </c>
+      <c r="V4">
         <v>9</v>
       </c>
     </row>
@@ -5870,57 +6088,55 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{323C6C67-687F-3242-B2A5-03764AF4AAC6}">
   <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="18">
+    <row r="1" spans="1:7">
+      <c r="A1">
         <v>2</v>
       </c>
-      <c r="B1" s="18">
+      <c r="B1">
         <v>6</v>
       </c>
-      <c r="D1" s="18">
+      <c r="D1">
         <v>2</v>
       </c>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18">
+      <c r="F1">
         <v>18</v>
       </c>
-      <c r="G1" s="18">
+      <c r="G1">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="18"/>
-      <c r="B2" s="18">
+    <row r="2" spans="1:7">
+      <c r="B2">
         <v>6</v>
       </c>
-      <c r="D2" s="18">
+      <c r="D2">
         <v>6</v>
       </c>
-      <c r="E2" s="18">
+      <c r="E2">
         <v>6</v>
       </c>
-      <c r="F2" s="18">
+      <c r="F2">
         <v>22</v>
       </c>
-      <c r="G2" s="18">
+      <c r="G2">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="18">
+    <row r="3" spans="1:7">
+      <c r="A3">
         <v>18</v>
       </c>
-      <c r="B3" s="18">
+      <c r="B3">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="18">
+    <row r="4" spans="1:7">
+      <c r="A4">
         <v>5</v>
       </c>
-      <c r="B4" s="18">
+      <c r="B4">
         <v>4</v>
       </c>
     </row>
@@ -5932,53 +6148,53 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{991EC56D-987A-0244-A99D-90F572F83166}">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="18">
+      <c r="B1">
         <v>21.98</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="15" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="16" t="s">
+    <row r="2" spans="1:7">
+      <c r="A2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="18">
+      <c r="B2">
         <v>559.57000000000005</v>
       </c>
-      <c r="D2" s="22">
+      <c r="D2" s="19">
         <v>21.98</v>
       </c>
-      <c r="E2" s="22">
+      <c r="E2" s="19">
         <v>559.57000000000005</v>
       </c>
-      <c r="F2" s="22">
+      <c r="F2" s="19">
         <v>53.46</v>
       </c>
-      <c r="G2" s="22">
+      <c r="G2" s="19">
         <v>559.57000000000005</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="16" t="s">
+    <row r="3" spans="1:7">
+      <c r="A3" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="18">
+      <c r="B3">
         <v>53.46</v>
       </c>
     </row>
@@ -5990,43 +6206,41 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16CD545E-3892-5646-AEAF-9138954159A2}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="18">
+    <row r="1" spans="1:6">
+      <c r="A1">
         <v>9.36</v>
       </c>
-      <c r="B1" s="18">
+      <c r="B1">
         <v>15.873333333333333</v>
       </c>
-      <c r="D1" s="18">
+      <c r="D1">
         <v>9.36</v>
       </c>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18">
+      <c r="F1">
         <v>24.939999999999998</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="18"/>
-      <c r="B2" s="18">
+    <row r="2" spans="1:6">
+      <c r="B2">
         <v>322.39500000000004</v>
       </c>
-      <c r="D2" s="18">
+      <c r="D2">
         <v>15.873333333333333</v>
       </c>
-      <c r="E2" s="18">
+      <c r="E2">
         <v>322.39500000000004</v>
       </c>
-      <c r="F2" s="18">
+      <c r="F2">
         <v>37.0075</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="18">
+    <row r="3" spans="1:6">
+      <c r="A3">
         <v>24.939999999999998</v>
       </c>
-      <c r="B3" s="18">
+      <c r="B3">
         <v>37.0075</v>
       </c>
     </row>
